--- a/src/data_update/update_cards.xlsx
+++ b/src/data_update/update_cards.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,139 +456,139 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MANTA-30759</t>
+          <t>TENSYLON-818</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Manta</t>
+          <t>Tensylon</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30759</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-818</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30993 - ALT</t>
+          <t>31070</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MANTA-30722</t>
+          <t>TENSYLON-815</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Manta</t>
+          <t>Tensylon</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30722</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-815</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>31122</t>
+          <t>30956</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MANTA-30670</t>
+          <t>TENSYLON-813</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Manta</t>
+          <t>Tensylon</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30670</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-813</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>31073</t>
+          <t>30949</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MANTA-30667</t>
+          <t>TENSYLON-805</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Manta</t>
+          <t>Tensylon</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30667</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-805</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>31070</t>
+          <t>30905</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MANTA-30650</t>
+          <t>TENSYLON-745</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Manta</t>
+          <t>Tensylon</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30650</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-745</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>31055</t>
+          <t>30529</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MANTA-30636</t>
+          <t>TENSYLON-739</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Manta</t>
+          <t>Tensylon</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30636</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-739</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>31041</t>
+          <t>30510</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MANTA-30543</t>
+          <t>MANTA-30759</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -598,19 +598,19 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30543</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30759</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30949</t>
+          <t>30993 - ALT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MANTA-30520</t>
+          <t>MANTA-30722</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -620,19 +620,19 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30520</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30722</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>30929</t>
+          <t>31122</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MANTA-30496</t>
+          <t>MANTA-30670</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -642,19 +642,19 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30496</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30670</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>30905</t>
+          <t>31073</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MANTA-30494</t>
+          <t>MANTA-30667</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -664,19 +664,19 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30494</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30667</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30903</t>
+          <t>31070</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MANTA-30458</t>
+          <t>MANTA-30650</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -686,19 +686,19 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30458</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30650</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>30871</t>
+          <t>31055</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MANTA-30447</t>
+          <t>MANTA-30636</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -708,19 +708,19 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30447</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30636</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>30860</t>
+          <t>31041</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MANTA-30435</t>
+          <t>MANTA-30543</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -730,19 +730,19 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30435</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30543</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>30848</t>
+          <t>30949</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MANTA-30419</t>
+          <t>MANTA-30520</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -752,19 +752,19 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30419</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30520</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>30832</t>
+          <t>30929</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MANTA-30403</t>
+          <t>MANTA-30496</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -774,19 +774,19 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30403</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30496</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>30816</t>
+          <t>30905</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MANTA-30346</t>
+          <t>MANTA-30494</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -796,19 +796,19 @@
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30346</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30494</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>30766</t>
+          <t>30903</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MANTA-30265</t>
+          <t>MANTA-30458</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -818,19 +818,19 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30265</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30458</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>30693</t>
+          <t>30871</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MANTA-30099</t>
+          <t>MANTA-30447</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -840,19 +840,19 @@
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30099</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30447</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>30556</t>
+          <t>30860</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MANTA-30072</t>
+          <t>MANTA-30435</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -862,32 +862,164 @@
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30072</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30435</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>30529</t>
+          <t>30848</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>MANTA-30419</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30419</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>30832</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MANTA-30403</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30403</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>30816</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MANTA-30346</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30346</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>30766</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MANTA-30265</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30265</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>30693</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MANTA-30099</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30099</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>30556</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MANTA-30072</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30072</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>30529</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>MANTA-30053</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30053</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>30510</t>
         </is>
@@ -915,6 +1047,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/data_update/update_cards.xlsx
+++ b/src/data_update/update_cards.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,21 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>SITUAÇÃO</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Veículo</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>DT. PREVISÃO ENTREGA</t>
         </is>
       </c>
@@ -474,6 +489,21 @@
           <t>31070</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MINI - COOPER 02 PORTAS HATCH - 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -496,6 +526,21 @@
           <t>30956</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>A Produzir</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>LAND ROVER - NEW DISCOVERY SUV - 2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -518,6 +563,21 @@
           <t>30949</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BMW - SERIE 3 SEDAN - 2026</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -540,6 +600,21 @@
           <t>30905</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>BMW - X3 SUV - 2026</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -562,6 +637,21 @@
           <t>30529</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>GWM - HAVAL H6 PHEV 19 - 2026</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -584,6 +674,21 @@
           <t>30510</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>GWM - WEY 07 SUV - 2026</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -606,6 +711,21 @@
           <t>30993 - ALT</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>BMW - X1 SUV - 2026</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -628,6 +748,21 @@
           <t>31122</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>TOYOTA - SW4 SUV - 2026</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -650,6 +785,21 @@
           <t>31073</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>GWM - HAVAL H6 HEV 2 - 2026</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -672,6 +822,21 @@
           <t>31070</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MINI - COOPER 02 PORTAS HATCH - 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -694,6 +859,21 @@
           <t>31055</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FORD - TERRITORY - 2026</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -716,6 +896,21 @@
           <t>31041</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FORD - MUSTANG GT - 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -738,6 +933,21 @@
           <t>30949</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>A Produzir</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>BMW - SERIE 3 SEDAN - 2026</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -760,6 +970,21 @@
           <t>30929</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>VOLVO - EX30 PLUS SUV - 2026</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -782,6 +1007,21 @@
           <t>30905</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>BMW - X3 SUV - 2026</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -804,6 +1044,21 @@
           <t>30903</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>TOYOTA - RAV4 HEV SUV - 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -826,6 +1081,21 @@
           <t>30871</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>GWM - HAVAL H6 PHEV 35 - 2026</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -848,6 +1118,21 @@
           <t>30860</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BMW - X2 SUV - 2026</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -870,6 +1155,21 @@
           <t>30848</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>JEEP - COMMANDER SUV - 2022</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -892,6 +1192,21 @@
           <t>30832</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LAND ROVER - NEW RANGE ROVER SPORT SUV - 2026</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -914,6 +1229,21 @@
           <t>30816</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>A Produzir</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>FIAT - PULSE - 2024</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -936,6 +1266,21 @@
           <t>30766</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>JEEP - COMMANDER SUV - 2026</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -958,6 +1303,21 @@
           <t>30693</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>FORD - NOVA RANGER PICK-UP - 2026</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -980,6 +1340,21 @@
           <t>30556</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>GWM - HAVAL H6 PHEV 19 - 2026</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1002,6 +1377,21 @@
           <t>30529</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>GWM - HAVAL H6 PHEV 19 - 2026</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1022,6 +1412,21 @@
       <c r="D27" t="inlineStr">
         <is>
           <t>30510</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>GWM - WEY 07 SUV - 2026</t>
         </is>
       </c>
     </row>

--- a/src/data_update/update_cards.xlsx
+++ b/src/data_update/update_cards.xlsx
@@ -415,6 +415,9 @@
   </sheetPr>
   <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
